--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileReconciliationDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileReconciliationDetailTemplate.xlsx
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -49,19 +56,13 @@
     <t>实际实重</t>
   </si>
   <si>
-    <t>实际计费重</t>
+    <t>实际体积重</t>
   </si>
   <si>
     <t>费用项</t>
   </si>
   <si>
     <t>费用金额</t>
-  </si>
-  <si>
-    <t>重量单位</t>
-  </si>
-  <si>
-    <t>kg</t>
   </si>
 </sst>
 </file>
@@ -1002,8 +1003,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
     <col min="2" max="2" width="10.875" customWidth="1"/>
@@ -1011,7 +1012,7 @@
     <col min="5" max="5" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1026,14 +1027,6 @@
       </c>
       <c r="E1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="6:6">
-      <c r="F2" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileReconciliationDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileReconciliationDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26205" windowHeight="7995"/>
+    <workbookView windowWidth="27945" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,16 +29,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -63,6 +56,21 @@
   </si>
   <si>
     <t>费用金额</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>币种</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1003,8 +1011,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
     <col min="2" max="2" width="10.875" customWidth="1"/>
@@ -1012,7 +1020,7 @@
     <col min="5" max="5" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1027,6 +1035,9 @@
       </c>
       <c r="E1" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileReconciliationDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileReconciliationDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11775"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>来源单号</t>
+  </si>
+  <si>
+    <t>物流运单号</t>
+  </si>
+  <si>
+    <t>业务单号</t>
+  </si>
+  <si>
+    <t>实际实重</t>
+  </si>
+  <si>
+    <t>实际体积重</t>
+  </si>
   <si>
     <r>
       <t>*</t>
@@ -42,20 +57,23 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>物流运单号</t>
+      <t>费用项</t>
     </r>
   </si>
   <si>
-    <t>实际实重</t>
-  </si>
-  <si>
-    <t>实际体积重</t>
-  </si>
-  <si>
-    <t>费用项</t>
-  </si>
-  <si>
-    <t>费用金额</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>费用金额</t>
+    </r>
   </si>
   <si>
     <r>
@@ -83,10 +101,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -563,141 +587,147 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1011,23 +1041,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="14.625" customWidth="1"/>
-    <col min="2" max="2" width="10.875" customWidth="1"/>
-    <col min="3" max="3" width="12.875" customWidth="1"/>
-    <col min="5" max="5" width="10.375" customWidth="1"/>
+    <col min="1" max="2" width="20.875" customWidth="1"/>
+    <col min="3" max="3" width="22.25" customWidth="1"/>
+    <col min="4" max="4" width="10.875" customWidth="1"/>
+    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="6" max="6" width="19.75" customWidth="1"/>
+    <col min="7" max="7" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -1036,8 +1068,14 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileReconciliationDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileReconciliationDetailTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>注意事项：序号一直时，将执行费用分摊逻辑</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>序号</t>
+    </r>
+  </si>
   <si>
     <t>来源单号</t>
   </si>
@@ -62,6 +80,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -77,6 +102,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -111,13 +143,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -717,17 +749,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1041,44 +1079,63 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="2" width="20.875" customWidth="1"/>
-    <col min="3" max="3" width="22.25" customWidth="1"/>
-    <col min="4" max="4" width="10.875" customWidth="1"/>
-    <col min="5" max="5" width="12.875" customWidth="1"/>
-    <col min="6" max="6" width="19.75" customWidth="1"/>
-    <col min="7" max="7" width="10.375" customWidth="1"/>
+    <col min="2" max="3" width="20.875" customWidth="1"/>
+    <col min="4" max="4" width="22.25" customWidth="1"/>
+    <col min="5" max="5" width="10.875" customWidth="1"/>
+    <col min="6" max="6" width="12.875" customWidth="1"/>
+    <col min="7" max="7" width="19.75" customWidth="1"/>
+    <col min="8" max="8" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileReconciliationDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileReconciliationDetailTemplate.xlsx
@@ -35,6 +35,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -65,6 +72,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -749,11 +763,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1094,26 +1105,26 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E2" t="s">
@@ -1122,13 +1133,13 @@
       <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
     </row>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileReconciliationDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileReconciliationDetailTemplate.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>注意事项：序号一直时，将执行费用分摊逻辑</t>
+    <t>注意事项：序号一致时，将执行费用分摊逻辑</t>
   </si>
   <si>
     <r>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileReconciliationDetailTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileReconciliationDetailTemplate.xlsx
@@ -1147,6 +1147,11 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
+      <formula1>"CZK,PLN,GBP,EUR,THB,BRL,MXN,INR,KES,KRW,MOP,HKD,IDR,PHP,JPY,CAD,SGD,CNY,USD,AUD,SEK,MYR,TWD,AED,DKK,RUB,ZAR,NOK,CHF,SAR,TRY,NZD,HUF,ILS,VND"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
